--- a/artfynd/A 28586-2022 artfynd.xlsx
+++ b/artfynd/A 28586-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28586-2022 artfynd.xlsx
+++ b/artfynd/A 28586-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111940951</v>
+        <v>111940979</v>
       </c>
       <c r="B2" t="n">
-        <v>56575</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>371547</v>
+        <v>371603</v>
       </c>
       <c r="R2" t="n">
-        <v>6396570</v>
+        <v>6396456</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,9 +757,25 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -782,6 +788,217 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>111940941</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Borås flygplats, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>371404</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6396514</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I ung, trivial tallskog.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Johan Svedholm</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johan Svedholm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>111940951</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Borås flygplats, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>371548</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6396571</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Svedholm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Svedholm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28586-2022 artfynd.xlsx
+++ b/artfynd/A 28586-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111940979</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111940941</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,8 +1014,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111940951</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>